--- a/content/KPIM/02_campaigns/01_Tobi_Posts/01_Tobi_Posts.xlsx
+++ b/content/KPIM/02_campaigns/01_Tobi_Posts/01_Tobi_Posts.xlsx
@@ -858,7 +858,7 @@
     <col width="17" customWidth="1" min="18" max="18"/>
     <col width="11" customWidth="1" min="19" max="19"/>
     <col width="11" customWidth="1" min="20" max="20"/>
-    <col width="12" customWidth="1" min="21" max="21"/>
+    <col width="14" customWidth="1" min="21" max="21"/>
     <col width="15" customWidth="1" min="22" max="22"/>
     <col width="10" customWidth="1" min="23" max="23"/>
     <col width="13" customWidth="1" min="24" max="24"/>
@@ -968,7 +968,7 @@
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>atlas_html</t>
+          <t>preview_html</t>
         </is>
       </c>
       <c r="V1" s="5" t="inlineStr">
@@ -1028,11 +1028,6 @@
           <t>ai-agent-la-gi</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Giải thích agent cho người mới</t>
-        </is>
-      </c>
       <c r="I2" t="inlineStr">
         <is>
           <t>2026-06-25</t>
@@ -1051,6 +1046,16 @@
       <c r="P2" t="inlineStr">
         <is>
           <t>x</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>assets/TOBI-001_ai-agent-la-gi/thumbnail.svg</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>assets/TOBI-001_ai-agent-la-gi/preview.html</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
@@ -1102,12 +1107,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>agent-kiem-chat-luong-du-lieu</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>Data quality auditor agent</t>
+          <t>agent-kiem-chat-luong</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1138,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1193,43 +1193,6 @@
         </is>
       </c>
     </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TOBI-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>https://ducnguyen.vn/atlas/ai/ai-agent-la-gi</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>https://youtu.be/DEMO-001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>100_123</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>https://facebook.com/DEMO-001</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>2026-06-25</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>published</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <autoFilter ref="A1:H1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1242,7 +1205,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:J1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1306,41 +1269,6 @@
       <c r="J1" s="1" t="inlineStr">
         <is>
           <t>fetched_at</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>TOBI-001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>100_123</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
-        <v>42</v>
-      </c>
-      <c r="E2" t="n">
-        <v>8</v>
-      </c>
-      <c r="F2" t="n">
-        <v>51</v>
-      </c>
-      <c r="G2" t="n">
-        <v>6</v>
-      </c>
-      <c r="H2" t="n">
-        <v>3200</v>
-      </c>
-      <c r="I2" t="n">
-        <v>4100</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>2026-07-23 18:42:47</t>
         </is>
       </c>
     </row>
@@ -1407,19 +1335,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>content_md</t>
+          <t>preview_html</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>assets/TOBI-001_ai-agent-la-gi/content.md</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+          <t>assets/TOBI-001_ai-agent-la-gi/preview.html</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-23 18:42:48</t>
+          <t>2026-07-23 19:10:03</t>
         </is>
       </c>
     </row>

--- a/content/KPIM/02_campaigns/01_Tobi_Posts/01_Tobi_Posts.xlsx
+++ b/content/KPIM/02_campaigns/01_Tobi_Posts/01_Tobi_Posts.xlsx
@@ -1138,7 +1138,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -1190,6 +1190,43 @@
       <c r="H1" s="1" t="inlineStr">
         <is>
           <t>status</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>TOBI-001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>https://ducnguyen.vn/atlas/ai/ai-agent-la-gi</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>https://youtu.be/DEMO-001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>100_123</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>https://facebook.com/DEMO-001</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>published</t>
         </is>
       </c>
     </row>
